--- a/parsers/data/raw/minfin/INTERNET_Auction_Results_rus_2026.xlsx
+++ b/parsers/data/raw/minfin/INTERNET_Auction_Results_rus_2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$A$3:$O$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$A$3:$O$64</definedName>
   </definedNames>
   <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="46">
   <si>
     <t>По состоянию на</t>
   </si>
@@ -747,7 +747,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <v>46163</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
@@ -3362,73 +3362,167 @@
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="10">
+        <v>46169</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="10">
+        <v>47723</v>
+      </c>
+      <c r="F61" s="12">
+        <v>1554</v>
+      </c>
+      <c r="G61" s="13">
+        <v>180047.48199999999</v>
+      </c>
+      <c r="H61" s="14">
+        <v>86.898499999999999</v>
+      </c>
+      <c r="I61" s="14">
+        <v>86.929699999999997</v>
+      </c>
+      <c r="J61" s="15">
+        <v>14.11</v>
+      </c>
+      <c r="K61" s="15">
+        <v>14.099999999999998</v>
+      </c>
+      <c r="L61" s="13">
+        <v>97552.521999999997</v>
+      </c>
+      <c r="M61" s="13">
+        <v>70001.356</v>
+      </c>
+      <c r="N61" s="13">
+        <v>62400.401532350006</v>
+      </c>
+      <c r="O61" s="16">
+        <v>0.71757607660825007</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
+        <v>46169</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="10">
+        <v>50845</v>
+      </c>
+      <c r="F62" s="12">
+        <v>4676</v>
+      </c>
+      <c r="G62" s="13">
+        <v>255418.55300000001</v>
+      </c>
+      <c r="H62" s="14">
+        <v>61.709800000000001</v>
+      </c>
+      <c r="I62" s="14">
+        <v>61.753599999999999</v>
+      </c>
+      <c r="J62" s="15">
+        <v>14.799999999999999</v>
+      </c>
+      <c r="K62" s="15">
+        <v>14.790000000000001</v>
+      </c>
+      <c r="L62" s="13">
+        <v>67460.241999999998</v>
+      </c>
+      <c r="M62" s="13">
+        <v>34982.453999999998</v>
+      </c>
+      <c r="N62" s="13">
+        <v>22023.419427669996</v>
+      </c>
+      <c r="O62" s="16">
+        <v>0.51856401582431322</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B63" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E63" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F63" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G61" s="13" t="s">
+      <c r="G63" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H61" s="14" t="s">
+      <c r="H63" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="I63" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="J61" s="15" t="s">
+      <c r="J63" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="K61" s="15" t="s">
+      <c r="K63" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="L61" s="13">
-        <v>4601198.8310000002</v>
-      </c>
-      <c r="M61" s="13">
-        <v>2887200.4480000003</v>
-      </c>
-      <c r="N61" s="13">
-        <v>2551950.6521594091</v>
-      </c>
-      <c r="O61" s="16">
-        <v>0.62748873805405869</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="19" t="s">
+      <c r="L63" s="13">
+        <v>4766211.5949999997</v>
+      </c>
+      <c r="M63" s="13">
+        <v>2992184.2580000004</v>
+      </c>
+      <c r="N63" s="13">
+        <v>2636374.4731194293</v>
+      </c>
+      <c r="O63" s="16">
+        <v>0.627790898150421</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="21"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O64" s="1"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="21"/>
+    </row>
+    <row r="66" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O66" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3443,7 +3537,7 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="A62:O62"/>
+    <mergeCell ref="A64:O64"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="K6:K7"/>
@@ -3453,6 +3547,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="3.9370078740157501E-2" bottom="3.9370078740157501E-2" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="85" fitToHeight="8" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="83" fitToHeight="8" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>